--- a/Styled_Hospital_CMMS_Gantt_Chart.xlsx
+++ b/Styled_Hospital_CMMS_Gantt_Chart.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="50">
   <si>
     <t xml:space="preserve">Hospital CMMS - Gantt Chart  Devicecare</t>
   </si>
@@ -133,16 +133,10 @@
     <t xml:space="preserve">Notification System</t>
   </si>
   <si>
-    <t xml:space="preserve">Testing &amp; Bug Fixing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Testing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deployment &amp; Final Presentation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Deployment</t>
+    <t xml:space="preserve">Testing &amp; Bug Fixing &amp;Deployment &amp; Final Presentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Testing &amp; Deployment</t>
   </si>
   <si>
     <t xml:space="preserve">Milestones</t>
@@ -231,7 +225,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -265,19 +259,13 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4B183"/>
-        <bgColor rgb="FFF4CCCC"/>
+        <bgColor rgb="FFFFD966"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFD966"/>
         <bgColor rgb="FFF4B183"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4CCCC"/>
-        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -330,72 +318,68 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -445,11 +429,11 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFA9D18E"/>
-      <rgbColor rgb="FFFFD966"/>
+      <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF9DC3E6"/>
       <rgbColor rgb="FFF4B183"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFF4CCCC"/>
+      <rgbColor rgb="FFFFD966"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -654,399 +638,385 @@
   <dimension ref="A1:P1048576"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="49.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="5" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="49.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="25.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="5" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="17.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P3" s="3" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="D4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="7"/>
+      <c r="D5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="7"/>
+      <c r="D7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" s="7"/>
+      <c r="D8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
+      <c r="D9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" s="7"/>
+      <c r="D10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K11" s="9"/>
+      <c r="D11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
+      <c r="D12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
     </row>
     <row r="13" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L13" s="9"/>
+      <c r="D13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L13" s="10"/>
     </row>
     <row r="14" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
+      <c r="D14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M15" s="9"/>
+      <c r="D15" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M15" s="10"/>
     </row>
     <row r="16" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
+      <c r="D16" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
     </row>
     <row r="17" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="N17" s="11"/>
+      <c r="D17" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="O18" s="13"/>
-    </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="3" t="s">
+      <c r="D18" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="O18" s="14"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4"/>
+    </row>
+    <row r="21" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="14" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="P19" s="15"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3"/>
-    </row>
-    <row r="22" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="16" t="s">
+      <c r="B22" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
+      <c r="A23" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
+      <c r="A24" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="1" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
+      <c r="A25" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
+      <c r="A26" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" s="0" t="s">
-        <v>51</v>
-      </c>
-    </row>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
